--- a/artfynd/A 14285-2026 artfynd.xlsx
+++ b/artfynd/A 14285-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132878485</v>
+        <v>132878447</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -720,7 +720,7 @@
         <v>759356</v>
       </c>
       <c r="R2" t="n">
-        <v>7176721</v>
+        <v>7176740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,30 +780,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132878869</v>
+        <v>132878466</v>
       </c>
       <c r="B3" t="n">
-        <v>91940</v>
+        <v>91937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -818,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759302</v>
+        <v>759373</v>
       </c>
       <c r="R3" t="n">
-        <v>7176657</v>
+        <v>7176722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132878466</v>
+        <v>132878753</v>
       </c>
       <c r="B4" t="n">
-        <v>91883</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759373</v>
+        <v>759333</v>
       </c>
       <c r="R4" t="n">
-        <v>7176722</v>
+        <v>7176709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,11 +993,11 @@
         <v>132876178</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1091,38 +1095,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132878753</v>
+        <v>132878455</v>
       </c>
       <c r="B6" t="n">
-        <v>91883</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1133,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759333</v>
+        <v>759380</v>
       </c>
       <c r="R6" t="n">
-        <v>7176709</v>
+        <v>7176723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,42 +1200,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132878720</v>
+        <v>132878485</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1239,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759345</v>
+        <v>759356</v>
       </c>
       <c r="R7" t="n">
-        <v>7176702</v>
+        <v>7176721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,17 +1280,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,42 +1305,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132881371</v>
+        <v>132878770</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1349,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759339</v>
+        <v>759330</v>
       </c>
       <c r="R8" t="n">
-        <v>7176776</v>
+        <v>7176720</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,17 +1385,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1416,32 +1410,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132878455</v>
+        <v>132878886</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759380</v>
+        <v>759266</v>
       </c>
       <c r="R9" t="n">
-        <v>7176723</v>
+        <v>7176650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,41 +1515,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132878447</v>
+        <v>132881325</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1563,7 +1558,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759356</v>
+        <v>759207</v>
       </c>
       <c r="R10" t="n">
         <v>7176740</v>
@@ -1601,13 +1596,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska hack i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1626,41 +1625,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132878886</v>
+        <v>132876088</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759266</v>
+        <v>759461</v>
       </c>
       <c r="R11" t="n">
-        <v>7176650</v>
+        <v>7176757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,13 +1706,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack på gran. Med kikare syns en rad av små hackhål.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132878770</v>
+        <v>132878502</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,30 +1746,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1773,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759330</v>
+        <v>759356</v>
       </c>
       <c r="R12" t="n">
-        <v>7176720</v>
+        <v>7176721</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,13 +1816,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1836,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132878709</v>
+        <v>132878720</v>
       </c>
       <c r="B13" t="n">
-        <v>91940</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,26 +1856,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1874,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759359</v>
+        <v>759345</v>
       </c>
       <c r="R13" t="n">
-        <v>7176701</v>
+        <v>7176702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,13 +1926,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1937,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132878502</v>
+        <v>132878847</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759356</v>
+        <v>759379</v>
       </c>
       <c r="R14" t="n">
-        <v>7176721</v>
+        <v>7176681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,6 +2062,226 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132881342</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>759211</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7176742</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132881371</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>759339</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7176776</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14285-2026 artfynd.xlsx
+++ b/artfynd/A 14285-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878466</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132876178</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878455</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878485</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878886</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881325</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132876088</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878502</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,6 +2012,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878720</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878847</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881342</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,8 +2357,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>